--- a/docs/excel/リリース手順書.xlsx
+++ b/docs/excel/リリース手順書.xlsx
@@ -34,7 +34,7 @@
     <t>版</t>
   </si>
   <si>
-    <t>0.1（リリース前の下書き）</t>
+    <t>0.2（リリース前の下書き。迷惑番号の確認を、登録フォームに統合）</t>
   </si>
   <si>
     <t>作成日</t>
@@ -79,7 +79,7 @@
     <t>画面</t>
   </si>
   <si>
-    <t>デザインの刷新、矢印のタブ、メモ風の一覧・詳細、迷惑番号のカード、最初の画面が「迷惑電話チェック」、登録フォームの URL が /register</t>
+    <t>デザインの刷新、矢印のタブ、メモ風の一覧・詳細、迷惑番号のカード、迷惑番号の確認を、登録フォームの電話番号の欄に統合（旧「迷惑電話チェック」の画面はなくなる）、最初の画面が「登録フォーム」（URL は /register）</t>
   </si>
   <si>
     <t>画面（S3・CloudFront）を入れ替える</t>
@@ -235,7 +235,7 @@
     <t>☐ 2章の 1〜4、6 を確認し、結果を書き込む</t>
   </si>
   <si>
-    <t>☐ docs/テスト項目書.md の「未実施」のうち、リリース前に行うものを実施する（特に A04・A05、B05・B07、C05〜C07・C10・C11、D01・D05、E05・E07・E08、G12、I02〜I04）</t>
+    <t>☐ docs/テスト項目書.md の「未実施」のうち、リリース前に行うものを実施する（特に A04・A05、C05〜C07・C10・C11、D01・D05、E05・E07・E08、G12、I02〜I04）</t>
   </si>
   <si>
     <t>☐ 画面の lint の既存エラー（J02）を、直すか、そのままにするかを決める</t>
@@ -370,7 +370,7 @@
     <t>画面を開く</t>
   </si>
   <si>
-    <t>最初の画面が「迷惑電話チェック」。矢印のタブが出る</t>
+    <t>最初の画面が「登録フォーム」。矢印のタブ（登録フォーム・伝言一覧・迷惑番号一覧）が出る</t>
   </si>
   <si>
     <t/>
@@ -388,7 +388,7 @@
     <t>P02</t>
   </si>
   <si>
-    <t>迷惑番号を1件登録（番号は、0000000000 のような架空のもの）→ 検索 → 着信を記録 → 削除</t>
+    <t>迷惑番号を1件登録（番号は、0000000000 のような架空のもの）→ 登録フォームの電話番号に入力して、赤い札が出る → 着信を記録 → 削除</t>
   </si>
   <si>
     <t>すべてできる。SnapStart 下でのエラーがない（2章の5）</t>
@@ -968,7 +968,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="52" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" ht="68" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>114</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" ht="52" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>121</v>
       </c>

--- a/docs/excel/リリース手順書.xlsx
+++ b/docs/excel/リリース手順書.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="160">
   <si>
     <t>伝言メモ リリース手順書</t>
   </si>
@@ -34,7 +34,7 @@
     <t>版</t>
   </si>
   <si>
-    <t>0.2（リリース前の下書き。迷惑番号の確認を、登録フォームに統合）</t>
+    <t>0.3（リリース前の下書き。登録フォームから、直接の登録もできる）</t>
   </si>
   <si>
     <t>作成日</t>
@@ -79,7 +79,7 @@
     <t>画面</t>
   </si>
   <si>
-    <t>デザインの刷新、矢印のタブ、メモ風の一覧・詳細、迷惑番号のカード、迷惑番号の確認を、登録フォームの電話番号の欄に統合（旧「迷惑電話チェック」の画面はなくなる）、最初の画面が「登録フォーム」（URL は /register）</t>
+    <t>デザインの刷新、矢印のタブ、メモ風の一覧・詳細、迷惑番号のカード、迷惑番号の確認を、登録フォームの電話番号の欄に統合（旧「迷惑電話チェック」の画面はなくなる）、登録フォームから、確認を通らずに伝言を登録できる「このまま伝言を登録する」、その場での迷惑番号の登録、最初の画面が「登録フォーム」（URL は /register）</t>
   </si>
   <si>
     <t>画面（S3・CloudFront）を入れ替える</t>
@@ -397,10 +397,19 @@
     <t>P03</t>
   </si>
   <si>
-    <t>伝言を1件登録</t>
+    <t>伝言を1件登録（「確認」→「最終OK」の形で）</t>
   </si>
   <si>
     <t>「Teamsへ通知しました。」。「71_伝言メモ」に届く。一覧に出る。削除できる</t>
+  </si>
+  <si>
+    <t>P03b</t>
+  </si>
+  <si>
+    <t>伝言を1件登録（「このまま伝言を登録する」の形で）</t>
+  </si>
+  <si>
+    <t>一覧に移り、「Teamsへ通知しました。」。「71_伝言メモ」に届く。削除できる</t>
   </si>
   <si>
     <t>P04</t>
@@ -1039,7 +1048,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -1062,7 +1071,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>117</v>
@@ -1070,7 +1079,7 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>117</v>
@@ -1078,7 +1087,7 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>117</v>
@@ -1086,7 +1095,7 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>117</v>
@@ -1131,7 +1140,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="68" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" ht="100" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
@@ -1639,7 +1648,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1733,7 +1742,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>127</v>
       </c>
@@ -1761,19 +1770,33 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+    <row r="12" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="B12" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
@@ -1794,54 +1817,54 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" ht="52" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1868,32 +1891,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/リリース手順書.xlsx
+++ b/docs/excel/リリース手順書.xlsx
@@ -34,7 +34,7 @@
     <t>版</t>
   </si>
   <si>
-    <t>0.3（リリース前の下書き。登録フォームから、直接の登録もできる）</t>
+    <t>0.4（リリース前の下書き。ボタンの色と配置を整理）</t>
   </si>
   <si>
     <t>作成日</t>
@@ -79,7 +79,7 @@
     <t>画面</t>
   </si>
   <si>
-    <t>デザインの刷新、矢印のタブ、メモ風の一覧・詳細、迷惑番号のカード、迷惑番号の確認を、登録フォームの電話番号の欄に統合（旧「迷惑電話チェック」の画面はなくなる）、登録フォームから、確認を通らずに伝言を登録できる「このまま伝言を登録する」、その場での迷惑番号の登録、最初の画面が「登録フォーム」（URL は /register）</t>
+    <t>デザインの刷新、矢印のタブ、メモ風の一覧・詳細、迷惑番号のカード、迷惑番号の確認を、登録フォームの電話番号の欄に統合（旧「迷惑電話チェック」の画面はなくなる）、登録フォームから、確認を通らずに伝言を登録できる「登録する」（確認画面なし）、その場での迷惑番号の登録、最初の画面が「登録フォーム」（URL は /register）</t>
   </si>
   <si>
     <t>画面（S3・CloudFront）を入れ替える</t>
@@ -406,7 +406,7 @@
     <t>P03b</t>
   </si>
   <si>
-    <t>伝言を1件登録（「このまま伝言を登録する」の形で）</t>
+    <t>伝言を1件登録（フォーム下の「登録する」の形で）</t>
   </si>
   <si>
     <t>一覧に移り、「Teamsへ通知しました。」。「71_伝言メモ」に届く。削除できる</t>
@@ -977,7 +977,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>

--- a/docs/excel/リリース手順書.xlsx
+++ b/docs/excel/リリース手順書.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="157">
   <si>
     <t>伝言メモ リリース手順書</t>
   </si>
@@ -34,7 +34,7 @@
     <t>版</t>
   </si>
   <si>
-    <t>0.4（リリース前の下書き。ボタンの色と配置を整理）</t>
+    <t>0.5（リリース前の下書き。確認画面・完了画面をなくした）</t>
   </si>
   <si>
     <t>作成日</t>
@@ -79,7 +79,7 @@
     <t>画面</t>
   </si>
   <si>
-    <t>デザインの刷新、矢印のタブ、メモ風の一覧・詳細、迷惑番号のカード、迷惑番号の確認を、登録フォームの電話番号の欄に統合（旧「迷惑電話チェック」の画面はなくなる）、登録フォームから、確認を通らずに伝言を登録できる「登録する」（確認画面なし）、その場での迷惑番号の登録、最初の画面が「登録フォーム」（URL は /register）</t>
+    <t>デザインの刷新、矢印のタブ、メモ風の一覧・詳細、迷惑番号のカード、迷惑番号の確認を、登録フォームの電話番号の欄に統合（旧「迷惑電話チェック」の画面はなくなる）、確認画面・完了画面をなくし、フォーム下の「登録する」で、直接、伝言を登録して、伝言一覧へ移る形に変更、その場での迷惑番号の登録、最初の画面が「登録フォーム」（URL は /register）</t>
   </si>
   <si>
     <t>画面（S3・CloudFront）を入れ替える</t>
@@ -397,19 +397,10 @@
     <t>P03</t>
   </si>
   <si>
-    <t>伝言を1件登録（「確認」→「最終OK」の形で）</t>
-  </si>
-  <si>
-    <t>「Teamsへ通知しました。」。「71_伝言メモ」に届く。一覧に出る。削除できる</t>
-  </si>
-  <si>
-    <t>P03b</t>
-  </si>
-  <si>
-    <t>伝言を1件登録（フォーム下の「登録する」の形で）</t>
-  </si>
-  <si>
-    <t>一覧に移り、「Teamsへ通知しました。」。「71_伝言メモ」に届く。削除できる</t>
+    <t>伝言を1件登録（フォーム下の「登録する」）</t>
+  </si>
+  <si>
+    <t>伝言一覧に移り、「Teamsへ通知しました。」と「Teamsで確認する →」。「71_伝言メモ」に届く。削除できる</t>
   </si>
   <si>
     <t>P04</t>
@@ -1048,7 +1039,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -1071,7 +1062,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>117</v>
@@ -1079,7 +1070,7 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>117</v>
@@ -1087,7 +1078,7 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>117</v>
@@ -1095,7 +1086,7 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>117</v>
@@ -1648,7 +1639,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1742,7 +1733,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>127</v>
       </c>
@@ -1770,33 +1761,19 @@
         <v>117</v>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+    <row r="13" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
@@ -1817,54 +1794,54 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" ht="52" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1891,32 +1868,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/リリース手順書.xlsx
+++ b/docs/excel/リリース手順書.xlsx
@@ -7,7 +7,7 @@
     <sheet sheetId="1" name="概要" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="1. 今回のリリースの内容" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="2. リリース前に確かめること（ブロッカー）" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="3. 本番の Terraform に足す内容（案）" state="visible" r:id="rId7"/>
+    <sheet sheetId="4" name="3. 本番の Terraform への追加（書いた。適用" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="4. 事前準備（リリースの前日まで）" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="5. リリースの手順" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="6. リリース後の確認（本番）" state="visible" r:id="rId10"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="165">
   <si>
     <t>伝言メモ リリース手順書</t>
   </si>
@@ -34,7 +34,7 @@
     <t>版</t>
   </si>
   <si>
-    <t>0.5（リリース前の下書き。確認画面・完了画面をなくした）</t>
+    <t>0.6（リリース前の下書き。本番の Terraform への追加を、書いた（適用はしていない））</t>
   </si>
   <si>
     <t>作成日</t>
@@ -160,7 +160,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>CloudFront が、/nuisance・/register・/list などを直接開いたり、再読み込みしたりしても、画面を返す設定か（エラー時に index.html を返す設定）</t>
+    <t>（terraform/main.tf の CloudFront に、エラー時に index.html を返す設定がない。コンソールで足してあるか、確認する） CloudFront が、/nuisance・/register・/list などを直接開いたり、再読み込みしたりしても、画面を返す設定か（エラー時に index.html を返す設定）</t>
   </si>
   <si>
     <t>AWS コンソール（CloudFront の「エラーページ」）または、本番のテスト</t>
@@ -211,22 +211,46 @@
     <t>1 が分からない場合の選択肢（担当者が決める）: ①前任者から state をもらう ②既存の資源を terraform import で取り込み直す ③本番の追加分（表・ルート・環境変数・CORS）を、AWS コンソールで手作業で足す。③は、Terraform とコンソールの内容がずれるので、あとで取り込み直す前提にする。</t>
   </si>
   <si>
-    <t>3. 本番の Terraform に足す内容（案）</t>
-  </si>
-  <si>
-    <t>terraform/main.tf に、次を足す（まだ書き込んでいない。state が分かってから反映する）。値は、terraform-test/main.tf と同じ形。</t>
-  </si>
-  <si>
-    <t>・DynamoDB テーブル: 名前 NuisanceNumbers、キー phoneNumber（文字列）、PAY_PER_REQUEST</t>
-  </si>
-  <si>
-    <t>・Lambda の環境変数: NUISANCE_TABLE = "NuisanceNumbers"（MESSAGES_TABLE・MEMBERS_TABLE は、足さなくてよい。未設定のときは、今の名前が使われる）</t>
-  </si>
-  <si>
-    <t>・API Gateway のルート6本: GET /nuisance、GET /nuisance/{phoneNumber}、POST /nuisance、PUT /nuisance/{phoneNumber}、DELETE /nuisance/{phoneNumber}、POST /nuisance/{phoneNumber}/logs</t>
-  </si>
-  <si>
-    <t>・CORS の allow_methods に PUT を足す</t>
+    <t>3. 本番の Terraform への追加（書いた。適用はしていない）</t>
+  </si>
+  <si>
+    <t>terraform/main.tf に、次を追加した（2026-10-20）。値は、terraform-test/main.tf と同じ形。terraform validate は、通っている。本番の AWS には、何もしていない。</t>
+  </si>
+  <si>
+    <t>・DynamoDB テーブル NuisanceNumbers（キー phoneNumber、PAY_PER_REQUEST）</t>
+  </si>
+  <si>
+    <t>・Lambda の環境変数 NUISANCE_TABLE（MESSAGES_TABLE・MEMBERS_TABLE は、足さない。未設定のときは、今の名前が使われる）</t>
+  </si>
+  <si>
+    <t>・API Gateway のルート6本（GET /nuisance、GET /nuisance/{phoneNumber}、POST /nuisance、PUT /nuisance/{phoneNumber}、DELETE /nuisance/{phoneNumber}、POST /nuisance/{phoneNumber}/logs）</t>
+  </si>
+  <si>
+    <t>・CORS の allow_methods に PUT</t>
+  </si>
+  <si>
+    <t>terraform plan（本番の state を用意したあと、担当者が実行）で、期待する差分: 追加（表1・ルート6）と、変更（Lambda のコードと環境変数、API の CORS）だけ。削除（destroy）や、Messages・Members の変更が出たら、適用しない。</t>
+  </si>
+  <si>
+    <t>CloudFront のエラー時の設定（2章の3）が、本番にないと分かった場合は、別の変更として、aws_cloudfront_distribution に、custom_error_response（403・404 → /index.html、200）を足す案がある。コンソールで、すでに足してある場合は、Terraform に足すと、差分が出るので、先に、前任者に確認する。</t>
+  </si>
+  <si>
+    <t>ビルドの記録（2026-10-20、コミット時点の feature/register-phone-check）</t>
+  </si>
+  <si>
+    <t>成果物</t>
+  </si>
+  <si>
+    <t>API の jar</t>
+  </si>
+  <si>
+    <t>backend/message-api/target/message-api-1.0-SNAPSHOT.jar（約16.5MB）。mvn package OK（単体テスト16件 OK）。迷惑番号のクラスが入っている。SHA-256 の先頭: 1f27545aaaea72f8</t>
+  </si>
+  <si>
+    <t>frontend/dist/（3ファイル＋アイコン、約300KB）。npm run build OK。本番の API の URL が入り、テスト用の URL は入っていない</t>
+  </si>
+  <si>
+    <t>リリースの直前に、必ず、作り直す（このあと、コードが変わったら、記録も、変わる）。</t>
   </si>
   <si>
     <t>4. 事前準備（リリースの前日まで）</t>
@@ -968,7 +992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1039,7 +1063,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -1057,39 +1081,39 @@
         <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1273,7 +1297,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" ht="52" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" ht="84" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>45</v>
       </c>
@@ -1366,43 +1390,121 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="110" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="3" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+    </row>
+    <row r="3" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+    </row>
+    <row r="6" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" ht="48" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>68</v>
       </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+    </row>
+    <row r="10" ht="48" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+    </row>
+    <row r="12" ht="64" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" ht="52" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" ht="52" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A19:C19"/>
+  </mergeCells>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
@@ -1420,67 +1522,67 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1501,132 +1603,132 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1649,7 +1751,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -1657,7 +1759,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -1665,105 +1767,105 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" ht="52" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1794,54 +1896,54 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" ht="52" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1868,32 +1970,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/リリース手順書.xlsx
+++ b/docs/excel/リリース手順書.xlsx
@@ -208,7 +208,7 @@
     <t>未実施</t>
   </si>
   <si>
-    <t>1 が分からない場合の選択肢（担当者が決める）: ①前任者から state をもらう ②既存の資源を terraform import で取り込み直す ③本番の追加分（表・ルート・環境変数・CORS）を、AWS コンソールで手作業で足す。③は、Terraform とコンソールの内容がずれるので、あとで取り込み直す前提にする。</t>
+    <t>1 が分からない場合の選択肢（担当者が決める）: ①前任者から state をもらう ②既存の資源を terraform import で取り込み直す ③本番の追加分（表・ルート・環境変数・CORS）を、AWS コンソールで手作業で足す。③は、Terraform とコンソールの内容がずれるので、あとで取り込み直す前提にする。③の手順は、docs/リリース手順書（手作業版）.md に書いた（変更前の記録・バックアップ、変更、確認、戻し方）。</t>
   </si>
   <si>
     <t>3. 本番の Terraform への追加（書いた。適用はしていない）</t>
